--- a/research/traditional_assets/database/data/mauritius/mauritius_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0344</v>
+        <v>0.075</v>
       </c>
       <c r="E2">
-        <v>-0.0032</v>
+        <v>0.132</v>
       </c>
       <c r="G2">
-        <v>0.4391675560298826</v>
+        <v>0.4406587166382737</v>
       </c>
       <c r="H2">
-        <v>0.4391675560298826</v>
+        <v>0.4406587166382737</v>
       </c>
       <c r="I2">
-        <v>0.4076840981856991</v>
+        <v>0.4196479273140262</v>
       </c>
       <c r="J2">
-        <v>0.40435553814355</v>
+        <v>0.4146669117652298</v>
       </c>
       <c r="K2">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="L2">
-        <v>0.4130202774813234</v>
+        <v>0.4400908574673481</v>
       </c>
       <c r="M2">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="N2">
-        <v>0.03947939262472885</v>
+        <v>0.03847019122609673</v>
       </c>
       <c r="O2">
-        <v>0.04702842377260982</v>
+        <v>0.04412903225806451</v>
       </c>
       <c r="P2">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="Q2">
-        <v>0.03947939262472885</v>
+        <v>0.03847019122609673</v>
       </c>
       <c r="R2">
-        <v>0.04702842377260982</v>
+        <v>0.04412903225806451</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>102.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V2">
-        <v>1.111713665943601</v>
+        <v>0.7919010123734533</v>
       </c>
       <c r="W2">
-        <v>2.236994219653179</v>
+        <v>1.832151300236407</v>
       </c>
       <c r="X2">
-        <v>0.07448806755135237</v>
+        <v>0.11767372410312</v>
       </c>
       <c r="Y2">
-        <v>2.162506152101827</v>
-      </c>
-      <c r="Z2">
-        <v>-4.512400674211413</v>
-      </c>
-      <c r="AA2">
-        <v>-1.824614202940074</v>
+        <v>1.714477576133287</v>
       </c>
       <c r="AB2">
-        <v>0.07389818433695594</v>
-      </c>
-      <c r="AC2">
-        <v>-1.89851238727703</v>
+        <v>0.1170324350880194</v>
       </c>
       <c r="AD2">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AG2">
-        <v>-101.15</v>
+        <v>-69.11</v>
       </c>
       <c r="AH2">
-        <v>0.01443078567610903</v>
+        <v>0.01430313782015744</v>
       </c>
       <c r="AI2">
-        <v>0.02719033232628399</v>
+        <v>0.02243868498869369</v>
       </c>
       <c r="AJ2">
-        <v>11.30167597765363</v>
+        <v>-3.492167761495704</v>
       </c>
       <c r="AK2">
-        <v>1.913907284768212</v>
+        <v>5.353214562354765</v>
       </c>
       <c r="AL2">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="AM2">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="AN2">
-        <v>0.01741935483870968</v>
+        <v>0.01726907630522088</v>
       </c>
       <c r="AO2">
-        <v>2064.864864864865</v>
+        <v>6158.333333333334</v>
       </c>
       <c r="AP2">
-        <v>-1.305161290322581</v>
+        <v>-0.9251673360107094</v>
       </c>
       <c r="AQ2">
-        <v>2064.864864864865</v>
+        <v>6158.333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0344</v>
+        <v>0.075</v>
       </c>
       <c r="E3">
-        <v>-0.0032</v>
+        <v>0.132</v>
       </c>
       <c r="G3">
-        <v>0.4391675560298826</v>
+        <v>0.4406587166382737</v>
       </c>
       <c r="H3">
-        <v>0.4391675560298826</v>
+        <v>0.4406587166382737</v>
       </c>
       <c r="I3">
-        <v>0.4076840981856991</v>
+        <v>0.4196479273140262</v>
       </c>
       <c r="J3">
-        <v>0.40435553814355</v>
+        <v>0.4146669117652298</v>
       </c>
       <c r="K3">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="L3">
-        <v>0.4130202774813234</v>
+        <v>0.4400908574673481</v>
       </c>
       <c r="M3">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="N3">
-        <v>0.03947939262472885</v>
+        <v>0.03847019122609673</v>
       </c>
       <c r="O3">
-        <v>0.04702842377260982</v>
+        <v>0.04412903225806451</v>
       </c>
       <c r="P3">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="Q3">
-        <v>0.03947939262472885</v>
+        <v>0.03847019122609673</v>
       </c>
       <c r="R3">
-        <v>0.04702842377260982</v>
+        <v>0.04412903225806451</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>102.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V3">
-        <v>1.111713665943601</v>
+        <v>0.7919010123734533</v>
       </c>
       <c r="W3">
-        <v>2.236994219653179</v>
+        <v>1.832151300236407</v>
       </c>
       <c r="X3">
-        <v>0.07448806755135237</v>
+        <v>0.11767372410312</v>
       </c>
       <c r="Y3">
-        <v>2.162506152101827</v>
-      </c>
-      <c r="Z3">
-        <v>-4.512400674211413</v>
-      </c>
-      <c r="AA3">
-        <v>-1.824614202940074</v>
+        <v>1.714477576133287</v>
       </c>
       <c r="AB3">
-        <v>0.07389818433695594</v>
-      </c>
-      <c r="AC3">
-        <v>-1.89851238727703</v>
+        <v>0.1170324350880194</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AG3">
-        <v>-101.15</v>
+        <v>-69.11</v>
       </c>
       <c r="AH3">
-        <v>0.01443078567610903</v>
+        <v>0.01430313782015744</v>
       </c>
       <c r="AI3">
-        <v>0.02719033232628399</v>
+        <v>0.02243868498869369</v>
       </c>
       <c r="AJ3">
-        <v>11.30167597765363</v>
+        <v>-3.492167761495704</v>
       </c>
       <c r="AK3">
-        <v>1.913907284768212</v>
+        <v>5.353214562354765</v>
       </c>
       <c r="AL3">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="AN3">
-        <v>0.01741935483870968</v>
+        <v>0.01726907630522088</v>
       </c>
       <c r="AO3">
-        <v>2064.864864864865</v>
+        <v>6158.333333333334</v>
       </c>
       <c r="AP3">
-        <v>-1.305161290322581</v>
+        <v>-0.9251673360107094</v>
       </c>
       <c r="AQ3">
-        <v>2064.864864864865</v>
+        <v>6158.333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mauritius/mauritius_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.075</v>
+        <v>0.0757</v>
       </c>
       <c r="E2">
-        <v>0.132</v>
+        <v>0.118</v>
       </c>
       <c r="G2">
-        <v>0.4406587166382737</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="H2">
-        <v>0.4406587166382737</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="I2">
-        <v>0.4196479273140262</v>
+        <v>0.4589371980676328</v>
       </c>
       <c r="J2">
-        <v>0.4146669117652298</v>
+        <v>0.4553140096618357</v>
       </c>
       <c r="K2">
-        <v>77.5</v>
+        <v>93.2</v>
       </c>
       <c r="L2">
-        <v>0.4400908574673481</v>
+        <v>0.4502415458937198</v>
       </c>
       <c r="M2">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="N2">
-        <v>0.03847019122609673</v>
+        <v>0.03530591775325978</v>
       </c>
       <c r="O2">
-        <v>0.04412903225806451</v>
+        <v>0.03776824034334764</v>
       </c>
       <c r="P2">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="Q2">
-        <v>0.03847019122609673</v>
+        <v>0.03530591775325978</v>
       </c>
       <c r="R2">
-        <v>0.04412903225806451</v>
+        <v>0.03776824034334764</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,64 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>70.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="V2">
-        <v>0.7919010123734533</v>
+        <v>0.8425275827482447</v>
       </c>
       <c r="W2">
-        <v>1.832151300236407</v>
+        <v>1.875251509054326</v>
       </c>
       <c r="X2">
-        <v>0.11767372410312</v>
+        <v>0.100226582368263</v>
       </c>
       <c r="Y2">
-        <v>1.714477576133287</v>
+        <v>1.775024926686063</v>
       </c>
       <c r="AB2">
-        <v>0.1170324350880194</v>
+        <v>0.09983456200323174</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AG2">
-        <v>-69.11</v>
+        <v>-82.84999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.01430313782015744</v>
+        <v>0.01140307387208726</v>
       </c>
       <c r="AI2">
-        <v>0.02243868498869369</v>
+        <v>0.01565690946221919</v>
       </c>
       <c r="AJ2">
-        <v>-3.492167761495704</v>
+        <v>-4.916913946587535</v>
       </c>
       <c r="AK2">
-        <v>5.353214562354765</v>
+        <v>7.85308056872038</v>
       </c>
       <c r="AL2">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AM2">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AN2">
-        <v>0.01726907630522088</v>
+        <v>0.01200417536534447</v>
       </c>
       <c r="AO2">
-        <v>6158.333333333334</v>
+        <v>7307.692307692308</v>
       </c>
       <c r="AP2">
-        <v>-0.9251673360107094</v>
+        <v>-0.8648225469728601</v>
       </c>
       <c r="AQ2">
-        <v>6158.333333333334</v>
+        <v>7307.692307692308</v>
       </c>
     </row>
     <row r="3">
@@ -713,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.075</v>
+        <v>0.0757</v>
       </c>
       <c r="E3">
-        <v>0.132</v>
+        <v>0.118</v>
       </c>
       <c r="G3">
-        <v>0.4406587166382737</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="H3">
-        <v>0.4406587166382737</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="I3">
-        <v>0.4196479273140262</v>
+        <v>0.4589371980676328</v>
       </c>
       <c r="J3">
-        <v>0.4146669117652298</v>
+        <v>0.4553140096618357</v>
       </c>
       <c r="K3">
-        <v>77.5</v>
+        <v>93.2</v>
       </c>
       <c r="L3">
-        <v>0.4400908574673481</v>
+        <v>0.4502415458937198</v>
       </c>
       <c r="M3">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="N3">
-        <v>0.03847019122609673</v>
+        <v>0.03530591775325978</v>
       </c>
       <c r="O3">
-        <v>0.04412903225806451</v>
+        <v>0.03776824034334764</v>
       </c>
       <c r="P3">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="Q3">
-        <v>0.03847019122609673</v>
+        <v>0.03530591775325978</v>
       </c>
       <c r="R3">
-        <v>0.04412903225806451</v>
+        <v>0.03776824034334764</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,64 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>70.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="V3">
-        <v>0.7919010123734533</v>
+        <v>0.8425275827482447</v>
       </c>
       <c r="W3">
-        <v>1.832151300236407</v>
+        <v>1.875251509054326</v>
       </c>
       <c r="X3">
-        <v>0.11767372410312</v>
+        <v>0.100226582368263</v>
       </c>
       <c r="Y3">
-        <v>1.714477576133287</v>
+        <v>1.775024926686063</v>
       </c>
       <c r="AB3">
-        <v>0.1170324350880194</v>
+        <v>0.09983456200323174</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AG3">
-        <v>-69.11</v>
+        <v>-82.84999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.01430313782015744</v>
+        <v>0.01140307387208726</v>
       </c>
       <c r="AI3">
-        <v>0.02243868498869369</v>
+        <v>0.01565690946221919</v>
       </c>
       <c r="AJ3">
-        <v>-3.492167761495704</v>
+        <v>-4.916913946587535</v>
       </c>
       <c r="AK3">
-        <v>5.353214562354765</v>
+        <v>7.85308056872038</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AN3">
-        <v>0.01726907630522088</v>
+        <v>0.01200417536534447</v>
       </c>
       <c r="AO3">
-        <v>6158.333333333334</v>
+        <v>7307.692307692308</v>
       </c>
       <c r="AP3">
-        <v>-0.9251673360107094</v>
+        <v>-0.8648225469728601</v>
       </c>
       <c r="AQ3">
-        <v>6158.333333333334</v>
+        <v>7307.692307692308</v>
       </c>
     </row>
   </sheetData>
